--- a/Bus_Plan_Cleaned.xlsx
+++ b/Bus_Plan_Cleaned.xlsx
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>1.98</v>
+        <v>-157.5</v>
       </c>
       <c r="H31" t="n">
         <v>1</v>
